--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>ALVAREZ</t>
@@ -94,19 +88,16 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HIPOLITO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BRAVO</t>
   </si>
   <si>
     <t>RIVERA</t>
@@ -115,22 +106,16 @@
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>MENA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
-    <t>JOSE JULIAN</t>
-  </si>
-  <si>
-    <t>ALDO GEOVANNI</t>
+    <t>INGRID AMERICA</t>
   </si>
   <si>
     <t>PEDRO ANGEL</t>
@@ -139,10 +124,10 @@
     <t>DAVID OSWALDO</t>
   </si>
   <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
     <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
   </si>
 </sst>
 </file>
@@ -543,16 +528,16 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>67.5</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
         <v>6.3</v>
@@ -569,19 +554,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>70.45</v>
+        <v>77.27</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -595,19 +580,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>69.77</v>
+        <v>83.72</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -621,19 +606,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -686,16 +671,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.5</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -709,16 +697,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>77.27</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -732,16 +723,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.40000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -755,16 +749,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>13</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>61.9</v>
+      </c>
+      <c r="H5">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -817,19 +814,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>67.5</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -843,16 +840,16 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>70.45</v>
+        <v>77.27</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -869,19 +866,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>69.77</v>
+        <v>83.72</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -895,19 +892,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +914,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -949,39 +946,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920078</v>
+        <v>21330051920094</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -990,67 +987,67 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920092</v>
+        <v>21330051920135</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920098</v>
+        <v>21330051920136</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920135</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1059,76 +1056,30 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920136</v>
+        <v>21330051920038</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920038</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920105</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -91,10 +97,16 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
   </si>
   <si>
     <t>BRAVO</t>
@@ -112,6 +124,12 @@
     <t>TORRES</t>
   </si>
   <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
     <t>MIROSLAVA</t>
   </si>
   <si>
@@ -125,6 +143,9 @@
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ZAYRA</t>
@@ -914,7 +935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,108 +967,108 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920078</v>
+        <v>21330051920390</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920094</v>
+        <v>21330051920043</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920135</v>
+        <v>21330051920078</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920136</v>
+        <v>21330051920094</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1061,24 +1082,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920038</v>
+        <v>21330051920136</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920382</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920038</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
         <v>10</v>
       </c>
-      <c r="G7">
+      <c r="G10">
         <v>3</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,81 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>INGRID AMERICA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
 </sst>
 </file>
@@ -549,19 +474,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -575,19 +500,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -601,19 +526,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -627,19 +552,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -692,19 +617,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -718,19 +643,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -744,19 +669,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -770,19 +695,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -835,19 +760,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -861,19 +786,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -887,19 +812,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>83.72</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -913,19 +838,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -965,213 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920390</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920043</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920078</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920094</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920135</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920382</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920038</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
